--- a/activity/Population/PoblacionDANE.xlsx
+++ b/activity/Population/PoblacionDANE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29926"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.SIGE\activity\Population\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.SIGE\activity\Population\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EE6B33-0CE1-4DF5-AE01-7E4E00396D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" tabRatio="769" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" tabRatio="769" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Censal" sheetId="2" r:id="rId1"/>
@@ -1241,9 +1241,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1252,6 +1249,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1919,6 +1919,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1926,7 +1927,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3894,6 +3894,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3901,7 +3902,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4590,6 +4590,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4597,7 +4598,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6327,7 +6327,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="12229681" cy="6288593"/>
+    <xdr:ext cx="12228635" cy="6286500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -6686,23 +6686,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0463F7D-8A04-4EDE-8789-543ED0F016DA}">
   <dimension ref="A1:X26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="17.149999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.53515625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="9.921875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.61328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.4609375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.61328125" style="2" customWidth="1"/>
-    <col min="6" max="9" width="10.921875" style="2" customWidth="1"/>
-    <col min="10" max="12" width="10.4609375" style="2" customWidth="1"/>
-    <col min="13" max="14" width="9.15234375" style="2"/>
-    <col min="15" max="17" width="10.4609375" style="2" customWidth="1"/>
-    <col min="18" max="19" width="9.15234375" style="2"/>
-    <col min="20" max="22" width="10.4609375" style="2" customWidth="1"/>
-    <col min="23" max="16384" width="9.15234375" style="2"/>
+    <col min="1" max="1" width="9.53125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="9.9296875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="2" customWidth="1"/>
+    <col min="6" max="9" width="10.9296875" style="2" customWidth="1"/>
+    <col min="10" max="12" width="10.46484375" style="2" customWidth="1"/>
+    <col min="13" max="14" width="9.1328125" style="2"/>
+    <col min="15" max="17" width="10.46484375" style="2" customWidth="1"/>
+    <col min="18" max="19" width="9.1328125" style="2"/>
+    <col min="20" max="22" width="10.46484375" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
         <v>2</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A2" s="9" t="s">
         <v>65</v>
       </c>
@@ -6810,7 +6810,7 @@
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="str">
         <f>$A$2</f>
         <v>DANE</v>
@@ -6846,7 +6846,7 @@
       <c r="W3" s="9"/>
       <c r="X3" s="9"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="str">
         <f t="shared" ref="A4:A13" si="0">$A$2</f>
         <v>DANE</v>
@@ -6882,7 +6882,7 @@
       <c r="W4" s="9"/>
       <c r="X4" s="9"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -6918,7 +6918,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -6954,7 +6954,7 @@
       <c r="W6" s="9"/>
       <c r="X6" s="9"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -6990,7 +6990,7 @@
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7026,7 +7026,7 @@
       <c r="W8" s="9"/>
       <c r="X8" s="9"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7062,7 +7062,7 @@
       <c r="W9" s="9"/>
       <c r="X9" s="9"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7098,7 +7098,7 @@
       <c r="W10" s="9"/>
       <c r="X10" s="9"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7134,7 +7134,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="9"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7170,7 +7170,7 @@
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>DANE</v>
@@ -7206,7 +7206,7 @@
       <c r="W13" s="9"/>
       <c r="X13" s="9"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A14" s="11"/>
       <c r="B14" s="11"/>
       <c r="C14" s="9"/>
@@ -7232,7 +7232,7 @@
       <c r="W14" s="9"/>
       <c r="X14" s="9"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
       <c r="C15" s="9"/>
@@ -7258,7 +7258,7 @@
       <c r="W15" s="9"/>
       <c r="X15" s="9"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.45">
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -7282,7 +7282,7 @@
       <c r="W16" s="9"/>
       <c r="X16" s="9"/>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -7306,7 +7306,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
@@ -7330,7 +7330,7 @@
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
@@ -7354,7 +7354,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
@@ -7378,7 +7378,7 @@
       <c r="W20" s="9"/>
       <c r="X20" s="9"/>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -7402,7 +7402,7 @@
       <c r="W21" s="9"/>
       <c r="X21" s="9"/>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
@@ -7426,7 +7426,7 @@
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
@@ -7450,7 +7450,7 @@
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -7474,7 +7474,7 @@
       <c r="W24" s="9"/>
       <c r="X24" s="9"/>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
@@ -7498,7 +7498,7 @@
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
@@ -7532,20 +7532,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BF85B67-A9CB-4F86-9CEB-D63DBE20F700}">
   <dimension ref="B2:G23"/>
-  <sheetFormatPr defaultRowHeight="17.149999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="44" customWidth="1"/>
-    <col min="2" max="2" width="20.4609375" style="44" customWidth="1"/>
-    <col min="3" max="3" width="9.23046875" style="44"/>
+    <col min="1" max="1" width="2.6640625" style="44" customWidth="1"/>
+    <col min="2" max="2" width="20.46484375" style="44" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" style="44"/>
     <col min="4" max="4" width="5" style="44" customWidth="1"/>
-    <col min="5" max="5" width="18.3828125" style="44" customWidth="1"/>
-    <col min="6" max="6" width="9.23046875" style="44"/>
-    <col min="7" max="7" width="20.4609375" style="44" customWidth="1"/>
-    <col min="8" max="8" width="2.69140625" style="44" customWidth="1"/>
-    <col min="9" max="16384" width="9.23046875" style="44"/>
+    <col min="5" max="5" width="18.3984375" style="44" customWidth="1"/>
+    <col min="6" max="6" width="9.19921875" style="44"/>
+    <col min="7" max="7" width="20.46484375" style="44" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" style="44" customWidth="1"/>
+    <col min="9" max="16384" width="9.19921875" style="44"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B2" s="65" t="s">
         <v>54</v>
       </c>
@@ -7555,7 +7555,7 @@
       <c r="F2" s="65"/>
       <c r="G2" s="65"/>
     </row>
-    <row r="4" spans="2:7" ht="23.15" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:7" ht="24" x14ac:dyDescent="0.45">
       <c r="B4" s="45" t="s">
         <v>40</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:7" ht="18.75" x14ac:dyDescent="0.45">
       <c r="B5" s="45"/>
       <c r="C5" s="66" t="s">
         <v>45</v>
@@ -7580,7 +7580,7 @@
       <c r="E5" s="67"/>
       <c r="F5" s="68"/>
     </row>
-    <row r="6" spans="2:7" ht="26.6" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:7" ht="26.25" x14ac:dyDescent="0.45">
       <c r="B6" s="45"/>
       <c r="C6" s="35"/>
       <c r="D6" s="63">
@@ -7590,7 +7590,7 @@
       <c r="E6" s="64"/>
       <c r="F6" s="36"/>
     </row>
-    <row r="7" spans="2:7" ht="23.15" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" ht="24" x14ac:dyDescent="0.45">
       <c r="B7" s="45" t="s">
         <v>41</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="21" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="B8" s="45"/>
       <c r="C8" s="46" t="s">
         <v>39</v>
@@ -7617,7 +7617,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="34.299999999999997" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:7" ht="33" x14ac:dyDescent="0.45">
       <c r="B9" s="43" t="s">
         <v>58</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="21" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C10" s="46" t="s">
         <v>39</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
       <c r="C11" s="69" t="s">
         <v>44</v>
       </c>
@@ -7651,16 +7651,16 @@
       <c r="E11" s="70"/>
       <c r="F11" s="71"/>
     </row>
-    <row r="12" spans="2:7" ht="23.15" x14ac:dyDescent="0.4">
-      <c r="C12" s="60">
+    <row r="12" spans="2:7" ht="24" x14ac:dyDescent="0.45">
+      <c r="C12" s="59">
         <f>C9+F9</f>
         <v>912</v>
       </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="62"/>
-    </row>
-    <row r="13" spans="2:7" ht="21" x14ac:dyDescent="0.4">
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="61"/>
+    </row>
+    <row r="13" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C13" s="46" t="s">
         <v>39</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="36" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:7" ht="37.5" x14ac:dyDescent="0.45">
       <c r="B14" s="48" t="s">
         <v>55</v>
       </c>
@@ -7686,13 +7686,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="21" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C15" s="46"/>
       <c r="D15" s="46"/>
       <c r="E15" s="46"/>
       <c r="F15" s="46"/>
     </row>
-    <row r="16" spans="2:7" s="53" customFormat="1" ht="14.6" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:7" s="53" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
       <c r="B16" s="53" t="s">
         <v>47</v>
       </c>
@@ -7701,92 +7701,92 @@
       <c r="E16" s="54"/>
       <c r="F16" s="54"/>
     </row>
-    <row r="17" spans="2:7" s="51" customFormat="1" ht="14.6" x14ac:dyDescent="0.4">
-      <c r="B17" s="59" t="s">
+    <row r="17" spans="2:7" s="51" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B17" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
       <c r="G17" s="52">
         <f>(C12/F14)*1000</f>
         <v>7.0466065026579301</v>
       </c>
     </row>
-    <row r="18" spans="2:7" s="51" customFormat="1" ht="14.6" x14ac:dyDescent="0.4">
-      <c r="B18" s="59" t="s">
+    <row r="18" spans="2:7" s="51" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B18" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
       <c r="G18" s="52">
         <f>(C4/F14)*1000</f>
         <v>2.6424774384967242</v>
       </c>
     </row>
-    <row r="19" spans="2:7" s="51" customFormat="1" ht="14.6" x14ac:dyDescent="0.4">
-      <c r="B19" s="59" t="s">
+    <row r="19" spans="2:7" s="51" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B19" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
       <c r="G19" s="52">
         <f>(C7/F14)*1000</f>
         <v>0.49449870194090745</v>
       </c>
     </row>
-    <row r="20" spans="2:7" s="51" customFormat="1" ht="14.6" x14ac:dyDescent="0.4">
-      <c r="B20" s="59" t="s">
+    <row r="20" spans="2:7" s="51" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B20" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
       <c r="G20" s="52">
         <f>G18-G19</f>
         <v>2.1479787365558169</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B21" s="59" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B21" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
       <c r="G21" s="52">
         <f>(F4/F14)*1000</f>
         <v>7.5411052045988383</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="59" t="s">
+    <row r="22" spans="2:7" ht="17.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
       <c r="G22" s="52">
         <f>(F7/F14)*1000</f>
         <v>2.6424774384967242</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B23" s="59" t="s">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B23" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
       <c r="G23" s="52">
         <f>G21-G22</f>
         <v>4.8986277661021145</v>
@@ -7794,6 +7794,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
@@ -7801,11 +7806,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7814,29 +7814,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94697D0-7CF3-40B1-9A24-C33BBE54D035}">
   <dimension ref="B2:M38"/>
-  <sheetFormatPr defaultRowHeight="17.149999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.53515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.921875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.765625" style="2" customWidth="1"/>
-    <col min="5" max="13" width="11.61328125" style="2" customWidth="1"/>
-    <col min="14" max="18" width="9.23046875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="13.69140625" style="2" customWidth="1"/>
-    <col min="20" max="24" width="9.23046875" style="2" customWidth="1"/>
-    <col min="25" max="25" width="13.69140625" style="2" customWidth="1"/>
-    <col min="26" max="33" width="9.23046875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="12.921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.23046875" style="2" customWidth="1"/>
-    <col min="36" max="16384" width="9.23046875" style="2"/>
+    <col min="1" max="1" width="2.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.53125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.9296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.73046875" style="2" customWidth="1"/>
+    <col min="5" max="13" width="11.59765625" style="2" customWidth="1"/>
+    <col min="14" max="18" width="9.19921875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="13.6640625" style="2" customWidth="1"/>
+    <col min="20" max="24" width="9.19921875" style="2" customWidth="1"/>
+    <col min="25" max="25" width="13.6640625" style="2" customWidth="1"/>
+    <col min="26" max="33" width="9.19921875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="12.9296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.19921875" style="2" customWidth="1"/>
+    <col min="36" max="16384" width="9.19921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="2:13" s="1" customFormat="1" ht="34.299999999999997" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:13" s="1" customFormat="1" ht="33" x14ac:dyDescent="0.45">
       <c r="B3" s="72" t="s">
         <v>27</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B4" s="74"/>
       <c r="C4" s="75"/>
       <c r="D4" s="25" t="s">
@@ -7915,7 +7915,7 @@
         <v>2.7224153885616099E-2</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B5" s="74"/>
       <c r="C5" s="75"/>
       <c r="D5" s="25" t="s">
@@ -7958,7 +7958,7 @@
         <v>1.8412667744698342E-19</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B6" s="74"/>
       <c r="C6" s="75"/>
       <c r="D6" s="25" t="s">
@@ -7989,7 +7989,7 @@
       <c r="L6" s="23"/>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B7" s="74"/>
       <c r="C7" s="75"/>
       <c r="D7" s="25" t="s">
@@ -8017,7 +8017,7 @@
       <c r="L7" s="23"/>
       <c r="M7" s="24"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B8" s="74"/>
       <c r="C8" s="75"/>
       <c r="D8" s="25" t="s">
@@ -8042,7 +8042,7 @@
       <c r="L8" s="23"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B9" s="74"/>
       <c r="C9" s="75"/>
       <c r="D9" s="25" t="s">
@@ -8064,7 +8064,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="24"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B10" s="74"/>
       <c r="C10" s="75"/>
       <c r="D10" s="25" t="s">
@@ -8083,7 +8083,7 @@
       <c r="L10" s="23"/>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B11" s="74"/>
       <c r="C11" s="75"/>
       <c r="D11" s="26" t="s">
@@ -8126,7 +8126,7 @@
         <v>0.98965462686572325</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="34.299999999999997" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:13" ht="33" x14ac:dyDescent="0.45">
       <c r="B12" s="74"/>
       <c r="C12" s="75"/>
       <c r="D12" s="29" t="s">
@@ -8169,7 +8169,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B13" s="74"/>
       <c r="C13" s="75"/>
       <c r="D13" s="55" t="s">
@@ -8191,7 +8191,7 @@
       <c r="L13" s="57"/>
       <c r="M13" s="58"/>
     </row>
-    <row r="14" spans="2:13" ht="34.299999999999997" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:13" ht="33" x14ac:dyDescent="0.45">
       <c r="B14" s="76"/>
       <c r="C14" s="77"/>
       <c r="D14" s="19" t="s">
@@ -8209,12 +8209,12 @@
       <c r="L14" s="21"/>
       <c r="M14" s="22"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B16" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" spans="2:13" ht="34.299999999999997" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:13" ht="33" x14ac:dyDescent="0.45">
       <c r="B18" s="16" t="s">
         <v>2</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>Exponencial</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B19" s="56" t="s">
         <v>66</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>136886</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B20" s="17" t="str">
         <f>B19</f>
         <v>Proyectada</v>
@@ -8372,7 +8372,7 @@
         <v>156847</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B21" s="17" t="str">
         <f t="shared" ref="B21:B29" si="10">B20</f>
         <v>Proyectada</v>
@@ -8422,7 +8422,7 @@
         <v>179718</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" s="17" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8472,7 +8472,7 @@
         <v>205925</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" s="17" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8522,7 +8522,7 @@
         <v>235953</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B24" s="17" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8572,7 +8572,7 @@
         <v>270359</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="17" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8622,7 +8622,7 @@
         <v>309783</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B26" s="17" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8672,7 +8672,7 @@
         <v>354956</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B27" s="17" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8722,7 +8722,7 @@
         <v>406716</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B28" s="17" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8772,7 +8772,7 @@
         <v>466023</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B29" s="18" t="str">
         <f t="shared" si="10"/>
         <v>Proyectada</v>
@@ -8822,46 +8822,46 @@
         <v>533979</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
       <c r="D30" s="13"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B31" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D31" s="13"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B32" s="2" t="str">
         <f>_xlfn.CONCAT(Censal!A2," - Población censal ",Censal!B2," y población proyectada a ",D29-D19," años con diferentes tendencias")</f>
         <v>DANE - Población censal Municipio y población proyectada a 50 años con diferentes tendencias</v>
       </c>
       <c r="D32" s="13"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B33" s="2" t="str">
         <f>_xlfn.CONCAT(Censal!A2," - Población censal ",Censal!B2," y población proyectada a ",D29-D19," años para el ajuste seleccionado")</f>
         <v>DANE - Población censal Municipio y población proyectada a 50 años para el ajuste seleccionado</v>
       </c>
       <c r="D33" s="13"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="2" t="str">
         <f>_xlfn.CONCAT(Censal!A2," - Población censal municipal")</f>
         <v>DANE - Población censal municipal</v>
       </c>
       <c r="D34" s="13"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D35" s="13"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D36" s="13"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D37" s="13"/>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.45">
       <c r="D38" s="13"/>
     </row>
   </sheetData>
@@ -8876,16 +8876,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3DC757-E655-4AB9-91FA-E1AE22FE7E6A}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="17.149999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.23046875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.765625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.3046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.765625" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9.23046875" style="2"/>
+    <col min="1" max="1" width="14.19921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9.19921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="str">
         <f>Censal!A1</f>
         <v>Fuente</v>
@@ -8903,7 +8903,7 @@
         <v>PTotal</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="str">
         <f>Censal!A2</f>
         <v>DANE</v>
@@ -8921,7 +8921,7 @@
         <v>7108</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="str">
         <f>Censal!A3</f>
         <v>DANE</v>
@@ -8939,7 +8939,7 @@
         <v>11480</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="str">
         <f>Censal!A4</f>
         <v>DANE</v>
@@ -8957,7 +8957,7 @@
         <v>12273</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="str">
         <f>Censal!A5</f>
         <v>DANE</v>
@@ -8975,7 +8975,7 @@
         <v>20628</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="str">
         <f>Censal!A6</f>
         <v>DANE</v>
@@ -8993,7 +8993,7 @@
         <v>27775</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="str">
         <f>Censal!A7</f>
         <v>DANE</v>
@@ -9011,7 +9011,7 @@
         <v>39836</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="str">
         <f>Censal!A8</f>
         <v>DANE</v>
@@ -9029,7 +9029,7 @@
         <v>60202</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="str">
         <f>Censal!A9</f>
         <v>DANE</v>
@@ -9047,7 +9047,7 @@
         <v>69695</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="str">
         <f>Censal!A10</f>
         <v>DANE</v>
@@ -9065,7 +9065,7 @@
         <v>78923</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="str">
         <f>Censal!A11</f>
         <v>DANE</v>
@@ -9083,7 +9083,7 @@
         <v>100038</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="str">
         <f>Censal!A13</f>
         <v>DANE</v>
@@ -9101,7 +9101,7 @@
         <v>128968</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="str">
         <f>ProyectadaTotal!B19</f>
         <v>Proyectada</v>
@@ -9119,7 +9119,7 @@
         <v>127918</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="str">
         <f>ProyectadaTotal!B20</f>
         <v>Proyectada</v>
@@ -9137,7 +9137,7 @@
         <v>140346</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="str">
         <f>ProyectadaTotal!B21</f>
         <v>Proyectada</v>
@@ -9155,7 +9155,7 @@
         <v>153383</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="str">
         <f>ProyectadaTotal!B22</f>
         <v>Proyectada</v>
@@ -9173,7 +9173,7 @@
         <v>167026</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="str">
         <f>ProyectadaTotal!B23</f>
         <v>Proyectada</v>
@@ -9191,7 +9191,7 @@
         <v>181278</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="str">
         <f>ProyectadaTotal!B24</f>
         <v>Proyectada</v>
@@ -9209,7 +9209,7 @@
         <v>196136</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="str">
         <f>ProyectadaTotal!B25</f>
         <v>Proyectada</v>
@@ -9227,7 +9227,7 @@
         <v>211602</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="str">
         <f>ProyectadaTotal!B26</f>
         <v>Proyectada</v>
@@ -9245,7 +9245,7 @@
         <v>227676</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="str">
         <f>ProyectadaTotal!B27</f>
         <v>Proyectada</v>
@@ -9263,7 +9263,7 @@
         <v>244356</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="str">
         <f>ProyectadaTotal!B28</f>
         <v>Proyectada</v>
@@ -9281,7 +9281,7 @@
         <v>261645</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="str">
         <f>ProyectadaTotal!B29</f>
         <v>Proyectada</v>
